--- a/data/trans_dic/P62A$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,71</t>
+          <t>1,05; 8,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,44; 36,94</t>
+          <t>21,95; 37,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,15</t>
+          <t>0,0; 19,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 14,52</t>
+          <t>1,74; 15,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 31,3</t>
+          <t>15,24; 31,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,23</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,65</t>
+          <t>0,98; 9,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,41</t>
+          <t>1,37; 8,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 32,17</t>
+          <t>20,89; 32,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,75</t>
+          <t>1,25; 10,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,33; 40,64</t>
+          <t>25,45; 41,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 40,88</t>
+          <t>4,38; 40,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 43,23</t>
+          <t>9,79; 42,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 39,99</t>
+          <t>10,79; 42,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,43; 33,1</t>
+          <t>16,47; 33,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,47</t>
+          <t>1,17; 10,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,19</t>
+          <t>3,23; 14,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 17,07</t>
+          <t>5,08; 17,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,44; 35,25</t>
+          <t>24,39; 35,6</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,02</t>
+          <t>3,56; 11,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,37</t>
+          <t>3,55; 11,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,61</t>
+          <t>24,94; 38,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,74</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 23,51</t>
+          <t>2,13; 24,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 32,61</t>
+          <t>15,01; 32,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,81</t>
+          <t>3,43; 9,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 11,57</t>
+          <t>4,37; 12,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,62; 34,27</t>
+          <t>23,43; 34,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,35</t>
+          <t>0,24; 2,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,27</t>
+          <t>4,32; 10,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,31</t>
+          <t>6,06; 12,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 32,2</t>
+          <t>23,36; 32,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,22</t>
+          <t>3,28; 12,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,29; 38,42</t>
+          <t>20,67; 38,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 25,85</t>
+          <t>12,29; 25,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 27,3</t>
+          <t>2,31; 27,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,59</t>
+          <t>1,21; 3,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,36</t>
+          <t>9,96; 16,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,93</t>
+          <t>8,64; 14,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 27,78</t>
+          <t>6,99; 28,17</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,64</t>
+          <t>3,84; 12,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,63</t>
+          <t>2,09; 8,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,71; 40,58</t>
+          <t>26,46; 41,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,09</t>
+          <t>5,04; 12,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,96</t>
+          <t>8,57; 18,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,69; 29,08</t>
+          <t>20,41; 29,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,89</t>
+          <t>0,46; 5,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,11</t>
+          <t>5,61; 10,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,22</t>
+          <t>6,08; 11,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,57; 32,09</t>
+          <t>24,58; 31,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 54,94</t>
+          <t>5,57; 50,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,77</t>
+          <t>0,0; 61,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,23; 90,76</t>
+          <t>29,31; 89,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,43</t>
+          <t>2,11; 7,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,64</t>
+          <t>7,83; 15,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 21,69</t>
+          <t>11,47; 21,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,5</t>
+          <t>8,09; 15,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,03</t>
+          <t>2,17; 7,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 16,18</t>
+          <t>8,55; 16,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,01; 21,24</t>
+          <t>11,91; 20,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,48; 18,52</t>
+          <t>10,1; 18,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,7</t>
+          <t>0,37; 1,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,62</t>
+          <t>5,01; 8,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,32</t>
+          <t>4,94; 8,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27,95; 33,5</t>
+          <t>28,07; 33,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,74</t>
+          <t>3,0; 6,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,57</t>
+          <t>10,42; 15,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,33</t>
+          <t>11,81; 17,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 21,54</t>
+          <t>8,5; 21,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,64</t>
+          <t>1,86; 3,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,07</t>
+          <t>8,05; 11,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,8</t>
+          <t>8,74; 11,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,05; 26,59</t>
+          <t>14,17; 26,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que recibe otro tipo de pensión</t>
+          <t>Población que percibe otro tipo de pensión (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4635</t>
+          <t>0; 4792</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6412</t>
+          <t>0; 6998</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1036; 9537</t>
+          <t>1035; 8449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23248; 38269</t>
+          <t>22741; 38409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5140</t>
+          <t>0; 5106</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7132</t>
+          <t>0; 7288</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>868; 7205</t>
+          <t>862; 7818</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9740; 20092</t>
+          <t>9782; 20197</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6735</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1050; 10355</t>
+          <t>1052; 10487</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2002; 12426</t>
+          <t>2027; 12281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35152; 53981</t>
+          <t>35060; 54397</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6533</t>
+          <t>0; 5187</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>983; 7722</t>
+          <t>992; 8353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27303; 43803</t>
+          <t>27425; 44185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1053; 10572</t>
+          <t>1132; 10369</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3813; 16139</t>
+          <t>3656; 15727</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3842; 14550</t>
+          <t>3924; 15365</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10519; 19979</t>
+          <t>9943; 20251</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1020; 9649</t>
+          <t>1189; 10341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4104; 18830</t>
+          <t>4288; 19328</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5793; 19724</t>
+          <t>5865; 20443</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41098; 59268</t>
+          <t>41002; 59859</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5338</t>
+          <t>0; 6266</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7206; 22249</t>
+          <t>6584; 22158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5647; 19755</t>
+          <t>6176; 20020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32979; 50631</t>
+          <t>32700; 51110</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1834</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6918</t>
+          <t>0; 6699</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1032; 11539</t>
+          <t>1043; 12163</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7875; 16837</t>
+          <t>7748; 16732</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6091</t>
+          <t>0; 6001</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8063; 23930</t>
+          <t>8362; 24178</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9139; 25786</t>
+          <t>9729; 26745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43166; 62622</t>
+          <t>42819; 62780</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>873; 8491</t>
+          <t>866; 7458</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17270; 39406</t>
+          <t>15105; 36236</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20184; 42571</t>
+          <t>20943; 42710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68404; 95023</t>
+          <t>68932; 95666</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3610; 13806</t>
+          <t>3709; 14662</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24663; 44501</t>
+          <t>23948; 44769</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17617; 37374</t>
+          <t>17774; 37088</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8042; 90466</t>
+          <t>7647; 90041</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4896; 17036</t>
+          <t>5727; 17971</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45818; 76189</t>
+          <t>46356; 76453</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42472; 73179</t>
+          <t>42368; 71560</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44651; 174084</t>
+          <t>43801; 176478</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 5792</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6306; 19304</t>
+          <t>5864; 19381</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4428; 16707</t>
+          <t>4038; 16501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37680; 57248</t>
+          <t>37327; 58830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8890</t>
+          <t>0; 8471</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11867; 29667</t>
+          <t>11426; 29343</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17375; 37041</t>
+          <t>17680; 37686</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45822; 64389</t>
+          <t>45201; 64876</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>873; 10836</t>
+          <t>851; 10086</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20637; 42119</t>
+          <t>21268; 40821</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25297; 48866</t>
+          <t>24304; 47497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89070; 116339</t>
+          <t>89105; 115900</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1758</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>930; 8843</t>
+          <t>896; 8098</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5215</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3389; 9848</t>
+          <t>3180; 9678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6329; 20304</t>
+          <t>5773; 20824</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20616; 42105</t>
+          <t>21094; 42485</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29272; 53937</t>
+          <t>28530; 52279</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16011; 30395</t>
+          <t>15875; 30150</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5888; 19914</t>
+          <t>6142; 20561</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23914; 46170</t>
+          <t>24391; 47245</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30880; 54617</t>
+          <t>30629; 53933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21687; 38333</t>
+          <t>20911; 38121</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2687; 12510</t>
+          <t>2736; 12850</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43787; 74958</t>
+          <t>43562; 75107</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44882; 74836</t>
+          <t>44428; 76052</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220725; 264479</t>
+          <t>221608; 265026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18477; 38851</t>
+          <t>17283; 39179</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77770; 116024</t>
+          <t>77667; 116559</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89343; 127302</t>
+          <t>86734; 129242</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>79732; 199283</t>
+          <t>78643; 200472</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23379; 47818</t>
+          <t>24370; 47400</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130879; 178760</t>
+          <t>129974; 180710</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>144181; 192774</t>
+          <t>142751; 191506</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>258021; 455907</t>
+          <t>242979; 454750</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$otras-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>0,0; 9,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,61</t>
+          <t>1,05; 8,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,95; 37,07</t>
+          <t>22,0; 36,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,57</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,75</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 31,46</t>
+          <t>14,34; 29,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,78</t>
+          <t>1,02; 9,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,31</t>
+          <t>1,47; 8,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,89; 32,42</t>
+          <t>21,27; 31,79</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -862,37 +862,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,55</t>
+          <t>1,23; 10,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,45; 41,0</t>
+          <t>26,25; 41,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 40,1</t>
+          <t>4,06; 39,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 42,13</t>
+          <t>8,63; 41,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 42,23</t>
+          <t>10,69; 40,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 33,55</t>
+          <t>16,18; 33,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 14,56</t>
+          <t>3,53; 14,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 17,69</t>
+          <t>4,41; 16,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,39; 35,6</t>
+          <t>24,19; 34,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,97</t>
+          <t>3,55; 11,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,52</t>
+          <t>3,77; 11,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,94; 38,98</t>
+          <t>25,82; 39,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 24,78</t>
+          <t>2,08; 24,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 32,41</t>
+          <t>14,93; 32,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,91</t>
+          <t>3,12; 10,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,0</t>
+          <t>4,18; 11,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,43; 34,35</t>
+          <t>24,16; 34,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,06</t>
+          <t>0,24; 2,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,36</t>
+          <t>4,76; 11,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 12,35</t>
+          <t>6,14; 12,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,36; 32,41</t>
+          <t>24,13; 33,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,97</t>
+          <t>3,15; 11,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,67; 38,65</t>
+          <t>20,48; 38,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 25,65</t>
+          <t>12,03; 25,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 27,17</t>
+          <t>21,61; 33,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,79</t>
+          <t>1,19; 3,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,42</t>
+          <t>9,81; 16,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 14,6</t>
+          <t>8,71; 14,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 28,17</t>
+          <t>24,07; 31,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,69</t>
+          <t>3,43; 12,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,52</t>
+          <t>1,96; 8,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,46; 41,7</t>
+          <t>27,4; 42,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,95</t>
+          <t>5,12; 12,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,57; 18,28</t>
+          <t>8,39; 17,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,41; 29,3</t>
+          <t>21,42; 30,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,49</t>
+          <t>0,47; 5,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,76</t>
+          <t>5,45; 11,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,88</t>
+          <t>6,28; 12,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,58; 31,97</t>
+          <t>25,17; 32,95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,57; 50,31</t>
+          <t>5,88; 52,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,59</t>
+          <t>0,0; 61,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,31; 89,2</t>
+          <t>31,39; 87,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,62</t>
+          <t>2,28; 7,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,78</t>
+          <t>7,71; 15,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,47; 21,02</t>
+          <t>11,96; 21,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 15,37</t>
+          <t>8,02; 14,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,25</t>
+          <t>2,05; 6,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,55; 16,56</t>
+          <t>8,63; 17,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,91; 20,98</t>
+          <t>11,77; 21,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,1; 18,42</t>
+          <t>9,38; 17,03</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,75</t>
+          <t>0,37; 1,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,64</t>
+          <t>5,01; 8,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,46</t>
+          <t>5,13; 8,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 33,57</t>
+          <t>28,59; 34,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,8</t>
+          <t>3,25; 6,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,64</t>
+          <t>10,51; 15,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,59</t>
+          <t>11,9; 17,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 21,67</t>
+          <t>18,84; 23,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,61</t>
+          <t>1,8; 3,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,19</t>
+          <t>8,1; 11,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 11,72</t>
+          <t>8,75; 11,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,17; 26,52</t>
+          <t>24,54; 28,19</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>49469</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4792</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6998</t>
+          <t>0; 6571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1035; 8449</t>
+          <t>1035; 8647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22741; 38409</t>
+          <t>25723; 43179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 5207</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7288</t>
+          <t>0; 6428</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>862; 7818</t>
+          <t>0; 7016</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9782; 20197</t>
+          <t>10407; 21051</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6756</t>
+          <t>0; 6020</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1052; 10487</t>
+          <t>1095; 9969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2027; 12281</t>
+          <t>2169; 11963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35060; 54397</t>
+          <t>40319; 60252</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>54864</t>
         </is>
       </c>
     </row>
@@ -2140,57 +2140,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5187</t>
+          <t>0; 7656</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>992; 8353</t>
+          <t>976; 8217</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27425; 44185</t>
+          <t>30646; 48702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1132; 10369</t>
+          <t>1051; 10098</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3656; 15727</t>
+          <t>3220; 15578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3924; 15365</t>
+          <t>3890; 14640</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9943; 20251</t>
+          <t>11101; 22776</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1189; 10341</t>
+          <t>1190; 10341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4288; 19328</t>
+          <t>4679; 19306</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5865; 20443</t>
+          <t>5101; 19300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41002; 59859</t>
+          <t>44831; 64788</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>59119</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6266</t>
+          <t>0; 5398</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6584; 22158</t>
+          <t>6567; 21831</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6176; 20020</t>
+          <t>6544; 20119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32700; 51110</t>
+          <t>37023; 56873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6699</t>
+          <t>0; 5954</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1043; 12163</t>
+          <t>1022; 12241</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7748; 16732</t>
+          <t>8464; 18301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6001</t>
+          <t>0; 6060</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8362; 24178</t>
+          <t>7602; 24616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9729; 26745</t>
+          <t>9314; 26690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42819; 62780</t>
+          <t>48354; 69885</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>90951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>36844</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>113113</t>
+          <t>127795</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>866; 7458</t>
+          <t>867; 8765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15105; 36236</t>
+          <t>16663; 38672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20943; 42710</t>
+          <t>21216; 42252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68932; 95666</t>
+          <t>77587; 107085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3709; 14662</t>
+          <t>3558; 13520</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23948; 44769</t>
+          <t>23719; 44046</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17774; 37088</t>
+          <t>17386; 36318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7647; 90041</t>
+          <t>29749; 46260</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5727; 17971</t>
+          <t>5642; 17505</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46356; 76453</t>
+          <t>45673; 76055</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42368; 71560</t>
+          <t>42705; 73202</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43801; 176478</t>
+          <t>110513; 144224</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>52251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54773</t>
+          <t>61733</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>102002</t>
+          <t>113984</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 4381</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5864; 19381</t>
+          <t>5230; 19200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4038; 16501</t>
+          <t>3803; 16827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37327; 58830</t>
+          <t>41370; 64740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8471</t>
+          <t>0; 8439</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11426; 29343</t>
+          <t>11604; 28451</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17680; 37686</t>
+          <t>17309; 36632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45201; 64876</t>
+          <t>51911; 72809</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>851; 10086</t>
+          <t>865; 10633</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21268; 40821</t>
+          <t>20678; 41905</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24304; 47497</t>
+          <t>25128; 50623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89105; 115900</t>
+          <t>98973; 129587</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>29269</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>896; 8098</t>
+          <t>946; 8499</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5200</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3180; 9678</t>
+          <t>3272; 9145</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5773; 20824</t>
+          <t>6216; 19821</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21094; 42485</t>
+          <t>20768; 42822</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28530; 52279</t>
+          <t>29732; 54057</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15875; 30150</t>
+          <t>16950; 31113</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6142; 20561</t>
+          <t>5808; 19687</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24391; 47245</t>
+          <t>24627; 48535</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30629; 53933</t>
+          <t>30263; 55422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20911; 38121</t>
+          <t>20801; 37781</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241178</t>
+          <t>268454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>149828</t>
+          <t>166046</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>391007</t>
+          <t>434500</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2736; 12850</t>
+          <t>2688; 12922</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43562; 75107</t>
+          <t>43553; 74790</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44428; 76052</t>
+          <t>46121; 76128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221608; 265026</t>
+          <t>245914; 295727</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17283; 39179</t>
+          <t>18706; 40171</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77667; 116559</t>
+          <t>78302; 117625</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86734; 129242</t>
+          <t>87398; 128981</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>78643; 200472</t>
+          <t>148693; 184006</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24370; 47400</t>
+          <t>23667; 47146</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>129974; 180710</t>
+          <t>130806; 181534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142751; 191506</t>
+          <t>142932; 192327</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>242979; 454750</t>
+          <t>404697; 464903</t>
         </is>
       </c>
     </row>
